--- a/StructureDefinition-observation-timing-context-ext.xlsx
+++ b/StructureDefinition-observation-timing-context-ext.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-observation-timing-context-ext.xlsx
+++ b/StructureDefinition-observation-timing-context-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-observation-timing-context-ext.xlsx
+++ b/StructureDefinition-observation-timing-context-ext.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$8</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="119">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,6 +351,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t xml:space="preserve">ext-1
 </t>
   </si>
@@ -373,6 +376,16 @@
   </si>
   <si>
     <t>http://qualityregistry.org/ValueSet/assessment-context-vs</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
 </sst>
 </file>
@@ -697,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK7"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.2734375" customWidth="true" bestFit="true"/>
@@ -1345,7 +1358,7 @@
         <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>102</v>
@@ -1357,10 +1370,10 @@
         <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>101</v>
@@ -1368,13 +1381,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>102</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>76</v>
@@ -1396,7 +1409,7 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>105</v>
@@ -1429,11 +1442,11 @@
         <v>76</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y7" s="2"/>
       <c r="Z7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>76</v>
@@ -1460,17 +1473,122 @@
         <v>82</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>101</v>
       </c>
     </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK7">
+  <autoFilter ref="A1:AK8">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -1480,7 +1598,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI6">
+  <conditionalFormatting sqref="A2:AI7">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-observation-timing-context-ext.xlsx
+++ b/StructureDefinition-observation-timing-context-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-observation-timing-context-ext.xlsx
+++ b/StructureDefinition-observation-timing-context-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-observation-timing-context-ext.xlsx
+++ b/StructureDefinition-observation-timing-context-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
